--- a/case_studies/base_case_50_5_dd/2040/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2040/technologies.xlsx
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -691,13 +691,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>114.1</v>
+        <v>115.42</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>195.38</v>
+        <v>197.63</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>13.41</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
@@ -706,22 +706,22 @@
         <v>946.41</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>983.99</v>
+        <v>946.41</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>228.2</v>
+        <v>230.83</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>273.75</v>
+        <v>259.32</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>36.8</v>
+        <v>37.46</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>22.37</v>
+        <v>21.27</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>49.16</v>
+        <v>46.73</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>23.43</v>
+        <v>24.75</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -779,22 +779,22 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.61</v>
+        <v>0.32</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>17.75</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>37.72</v>
+        <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>35.22</v>
+        <v>32.33</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>48.42</v>
+        <v>44.45</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>7.07</v>
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>62.99</v>
+        <v>56.57</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>176.54</v>
+        <v>169.2</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
@@ -900,19 +900,19 @@
         <v>1369.36</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1374.75</v>
+        <v>1369.36</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>129.38</v>
+        <v>113.15</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>165.84</v>
+        <v>144.86</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>43.32</v>
@@ -924,10 +924,10 @@
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>14.73</v>
+        <v>0</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>0</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>109.13</v>
+        <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>241.1</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>132.21</v>
+        <v>136.97</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>130.11</v>
+        <v>136.97</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>62.79</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -1073,19 +1073,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>64.79000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>159.7</v>
+        <v>117.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
@@ -1100,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>163.99</v>
+        <v>133.98</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>163.99</v>
+        <v>139.37</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>45.81</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>45.81</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>59.12</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>18.48</v>
+        <v>19.77</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.14</v>
+        <v>15.94</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0.36</v>
+        <v>1.14</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>18.38</v>
+        <v>19.51</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>108.82</v>
+        <v>136.83</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>284.42</v>
+        <v>288.69</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1294,28 +1294,28 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>318.14</v>
+        <v>352.54</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>130.06</v>
+        <v>102.09</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>73.62</v>
+        <v>50.33</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>110.4</v>
+        <v>136.83</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>129.51</v>
+        <v>101.67</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2040/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2040/technologies.xlsx
@@ -970,10 +970,10 @@
         <v>216.89</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>745.4</v>
+        <v>643.22</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>745.4</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>136.97</v>
+        <v>136.9</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>136.97</v>
+        <v>136.9</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>91.76000000000001</v>
+        <v>59.47</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.88</v>
+        <v>69.53</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>117.8</v>
+        <v>118.43</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>565.33</v>
+        <v>396.62</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>565.33</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>133.98</v>
+        <v>134.08</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>139.37</v>
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9.16</v>
+        <v>9</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>28.97</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.77</v>
+        <v>19.92</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.94</v>
+        <v>16.12</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1218,7 +1218,7 @@
         <v>1.14</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.51</v>
+        <v>19.72</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>136.83</v>
+        <v>136.92</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>288.69</v>
+        <v>288.71</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1294,19 +1294,19 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>352.54</v>
+        <v>352.65</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>102.09</v>
+        <v>101.99</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>50.33</v>
+        <v>50.26</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>136.83</v>
+        <v>136.92</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>1.54</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>101.67</v>
+        <v>101.58</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2040/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2040/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>115.42</v>
+        <v>114.43</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>197.63</v>
+        <v>195.94</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>230.83</v>
+        <v>228.86</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>259.32</v>
+        <v>270.18</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>37.46</v>
+        <v>35.44</v>
       </c>
       <c r="S2" s="3" t="n">
         <v>21.27</v>
@@ -730,10 +730,10 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>46.73</v>
+        <v>69.83</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>24.75</v>
+        <v>16.44</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>216.89</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>38.39</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>643.22</v>
+        <v>745.4</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>745.4</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>136.9</v>
+        <v>136.2</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>136.9</v>
+        <v>136.2</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>59.47</v>
+        <v>91.61</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>69.53</v>
+        <v>67.83</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>118.43</v>
+        <v>117.74</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>396.62</v>
+        <v>565.33</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>565.33</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>134.08</v>
+        <v>133.83</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>139.37</v>
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>9</v>
+        <v>9.42</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>95.54000000000001</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>28.97</v>
+        <v>48.52</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.92</v>
+        <v>19.87</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>16.12</v>
+        <v>15.89</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>19.72</v>
+        <v>19.5</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>136.92</v>
+        <v>136.69</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>288.71</v>
+        <v>288.62</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1294,28 +1294,28 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>352.65</v>
+        <v>352.44</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>427.03</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>101.99</v>
+        <v>102.32</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>50.26</v>
+        <v>50.29</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>136.92</v>
+        <v>136.69</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>101.58</v>
+        <v>101.76</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2040/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2040/technologies.xlsx
@@ -691,10 +691,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>114.43</v>
+        <v>115.26</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>195.94</v>
+        <v>197.36</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -712,10 +712,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>228.86</v>
+        <v>230.52</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>270.18</v>
+        <v>261.04</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>35.44</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>136.2</v>
+        <v>136.61</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>136.2</v>
+        <v>136.61</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>

--- a/case_studies/base_case_50_5_dd/2040/technologies.xlsx
+++ b/case_studies/base_case_50_5_dd/2040/technologies.xlsx
@@ -873,7 +873,7 @@
         <v>39.95</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
